--- a/data/downloads/tjn-fsi.xlsx
+++ b/data/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-08T14:47:27+00:00</t>
+          <t>2026-05-08T15:03:47+00:00</t>
         </is>
       </c>
     </row>

--- a/data/downloads/tjn-fsi.xlsx
+++ b/data/downloads/tjn-fsi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-08T15:03:47+00:00</t>
+          <t>2026-05-09T00:29:54+00:00</t>
         </is>
       </c>
     </row>
